--- a/data/trending_integrated_20261022_14.xlsx
+++ b/data/trending_integrated_20261022_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3690</v>
+        <v>3665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.42%</t>
+          <t>'+18.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F2" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G2" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>78440390339</v>
+        <v>80465423356</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.72%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>1352</v>
+        <v>1381</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>551249840800</v>
+        <v>560639925550</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 어닝 서프라이즈 및 자사주 취득 공시로 주주 기대감 고조. MSCI 편입 예상.</t>
+          <t>삼성E&amp;A, 시장 기대 뛰어넘는 어닝 서프라이즈 발표. MSCI 편입 예상 및 자사주 취득 공시로 강세 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7370</v>
+        <v>7400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.66%</t>
+          <t>'+11.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9018182740</v>
+        <v>9061911390</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1670</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.73%</t>
+          <t>'+4.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>22237879730</v>
+        <v>22315264302</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>27566876924</v>
+        <v>27894188858</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17890</v>
+        <v>17840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.17%</t>
+          <t>'-0.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H7" t="n">
         <v>3.29</v>
@@ -1070,7 +1070,7 @@
         <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>72631648860</v>
+        <v>73535674575</v>
       </c>
       <c r="P7" t="n">
         <v>22450</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14700</v>
+        <v>14680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>37146951120</v>
+        <v>37525446045</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1222,13 +1222,13 @@
         <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="H9" t="n">
         <v>25.47</v>
@@ -1254,7 +1254,7 @@
         <v>25.45</v>
       </c>
       <c r="O9" t="n">
-        <v>14532276180</v>
+        <v>15082640085</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>LG디스플레이, 3분기 호실적 발표에도 불구하고 주가는 부진. 투자 및 턴어라운드 기대감 존재.</t>
+          <t>LG디스플레이, 실적 개선 발표에도 불구하고 주가 부진. 누적 투자 대비 낮은 수익률 지적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['호실적', '주가 부진', '턴어라운드']</t>
+          <t>['실적 개선', '순이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="H10" t="n">
         <v>13.09</v>
@@ -1346,7 +1346,7 @@
         <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>12114162050</v>
+        <v>12347278425</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9930</v>
+        <v>9960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
         <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H11" t="n">
         <v>5.87</v>
@@ -1438,7 +1438,7 @@
         <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>16475952025</v>
+        <v>16723483430</v>
       </c>
       <c r="P11" t="n">
         <v>14940</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214750</v>
+        <v>213750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.91%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="G12" t="n">
-        <v>1576</v>
+        <v>1597</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1687144344250</v>
+        <v>1759659518500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 전반의 하락세 및 정치적 이슈와 관련된 부정적 언급 다수. 삼성전자 자체 호재 언급은 미미.</t>
+          <t>삼성전자, 정치적 이슈와 연기금 매도세로 인한 하락세 지속. 정부의 증시 부양 의지 부족 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국내 증시', '정치적 이슈', '하락세']</t>
+          <t>['정치적 악재', '연기금 매도', '증시 부양']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1220500</v>
+        <v>13460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.68%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.33</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>555</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>1669</v>
+        <v>501</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>3.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>14310</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>14180</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>14830</v>
       </c>
       <c r="M13" t="n">
-        <v>1204000</v>
+        <v>13450</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2255382031500</v>
+        <v>109708434765</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>1640</v>
       </c>
       <c r="R13" t="n">
-        <v>-62000</v>
+        <v>-506000</v>
       </c>
       <c r="S13" t="n">
-        <v>-88000</v>
+        <v>-3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 이슈 및 개인적 투자 손실에 대한 부정적 감정 표출. 솔리다임 상장 추진 철회 소식.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 소식. AI 광통신 열풍 관련 기대감 상승.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '개인 투자', '솔리다임']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13480</v>
+        <v>1216000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.80%</t>
+          <t>'-6.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="G14" t="n">
-        <v>486</v>
+        <v>1687</v>
       </c>
       <c r="H14" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14310</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>14180</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>14830</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>13460</v>
+        <v>1204000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>108612157090</v>
+        <v>2315411282500</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-506000</v>
+        <v>-62000</v>
       </c>
       <c r="S14" t="n">
-        <v>-3000</v>
+        <v>-88000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 소식에 따른 기대감. AI 광통신 관련 뉴스와 함께 주가 흐름에 대한 다양한 의견.</t>
+          <t>SK하이닉스, 정치적 논란과 시장 불확실성으로 주가 급락. 투자자들의 실망감 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['정치적 논란', '주가 급락', '투자자 실망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14070</v>
+        <v>13940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.07%</t>
+          <t>'-6.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H15" t="n">
         <v>1.2</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>79316386620</v>
+        <v>80116831770</v>
       </c>
       <c r="P15" t="n">
         <v>28800</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10000</v>
+        <v>9980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-10.41%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>60075449725</v>
+        <v>60534843645</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>HT로보틱스, 급락 및 투기 과열 종목 지정에 따른 우려. 향후 주가 전망에 대한 부정적 의견 지배적.</t>
+          <t>HT로보틱스, 급등 후 조정 및 투자주의 종목 지정으로 인한 하락세. ESS 마진율 불확실성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['급락', '투기 과열', '신용 비율']</t>
+          <t>['투자주의', '주가 조정', 'ESS 마진율']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261022_14.xlsx
+++ b/data/trending_integrated_20261022_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>3662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.61%</t>
+          <t>'+18.51%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F2" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G2" t="n">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>80465423356</v>
+        <v>81255606792</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55400</v>
+        <v>55600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.14%</t>
+          <t>'+16.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
-        <v>1381</v>
+        <v>1390</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>560639925550</v>
+        <v>569080109050</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7400</v>
+        <v>7390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.11%</t>
+          <t>'+10.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9061911390</v>
+        <v>9161484460</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1674</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.84%</t>
+          <t>'+3.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>22315264302</v>
+        <v>22416693408</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+2.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>27894188858</v>
+        <v>28019066672</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -1023,92 +1023,92 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17840</v>
+        <v>7290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.32</v>
+        <v>0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>720</v>
       </c>
       <c r="H7" t="n">
-        <v>3.29</v>
+        <v>25.47</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17920</v>
+        <v>7350</v>
       </c>
       <c r="K7" t="n">
-        <v>19180</v>
+        <v>7270</v>
       </c>
       <c r="L7" t="n">
-        <v>20150</v>
+        <v>7340</v>
       </c>
       <c r="M7" t="n">
-        <v>17690</v>
+        <v>7120</v>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>25.45</v>
       </c>
       <c r="O7" t="n">
-        <v>73535674575</v>
+        <v>15522199325</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>6320</v>
+        <v>7120</v>
       </c>
       <c r="R7" t="n">
-        <v>-37000</v>
+        <v>-148000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
+          <t>분기 순이익 7천억 달성에도 불구하고 주가 부진. 실적 개선세와 저평가 가능성 언급, 30년 최저가 근접 상황.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
+          <t>['흑자 전환', '당기순이익', '실적 개선']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14680</v>
+        <v>14640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
         <v>258</v>
@@ -1162,7 +1162,7 @@
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>37525446045</v>
+        <v>38161231105</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,92 +1207,92 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7300</v>
+        <v>17620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-1.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>682</v>
+        <v>131</v>
       </c>
       <c r="H9" t="n">
-        <v>25.47</v>
+        <v>3.29</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7350</v>
+        <v>17920</v>
       </c>
       <c r="K9" t="n">
-        <v>7270</v>
+        <v>19180</v>
       </c>
       <c r="L9" t="n">
-        <v>7340</v>
+        <v>20150</v>
       </c>
       <c r="M9" t="n">
-        <v>7120</v>
+        <v>17590</v>
       </c>
       <c r="N9" t="n">
-        <v>25.45</v>
+        <v>3.61</v>
       </c>
       <c r="O9" t="n">
-        <v>15082640085</v>
+        <v>74272236560</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>7120</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-148000</v>
+        <v>-37000</v>
       </c>
       <c r="S9" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>LG디스플레이, 실적 개선 발표에도 불구하고 주가 부진. 누적 투자 대비 낮은 수익률 지적.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적 개선', '순이익', '주가 부진']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41400</v>
+        <v>41350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.24%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G10" t="n">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="H10" t="n">
         <v>13.09</v>
@@ -1346,7 +1346,7 @@
         <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>12347278425</v>
+        <v>12657920550</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, 간암 치료제 FDA 승인 기대감 속에서 기관 매수세 확인. 결과 발표를 앞두고 신중론과 기대감이 혼재.</t>
+          <t>FDA 승인 기대감 속 기관 매수세 유입 관찰. C2 발표 가능성 및 클래스 1 기대감 언급, 시장의 흔들림에 대한 경계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['간암 치료제', 'FDA 승인', '기관 매수']</t>
+          <t>['FDA 승인', '간암 치료제', '기대감']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9960</v>
+        <v>9880</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
         <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="H11" t="n">
         <v>5.87</v>
@@ -1438,7 +1438,7 @@
         <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>16723483430</v>
+        <v>17007785585</v>
       </c>
       <c r="P11" t="n">
         <v>14940</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213750</v>
+        <v>213500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-4.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G12" t="n">
-        <v>1597</v>
+        <v>1645</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1524,13 +1524,13 @@
         <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>213500</v>
+        <v>213000</v>
       </c>
       <c r="N12" t="n">
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1759659518500</v>
+        <v>1813787252750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 연기금 매도세로 인한 하락세 지속. 정부의 증시 부양 의지 부족 지적.</t>
+          <t>주가 하락에도 정부의 대책 부재와 정치적 이슈로 인한 시장 불신 심화. 엔비디아, 마이크론 등 해외 증시와 상반된 국내 증시 흐름 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치적 악재', '연기금 매도', '증시 부양']</t>
+          <t>['주가 폭락', '정부 대책', '국내 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13460</v>
+        <v>14290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-4.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>501</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>3.48</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14310</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>14180</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>14830</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>13450</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>109708434765</v>
+        <v>81374872945</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>1640</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-506000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 소식. AI 광통신 열풍 관련 기대감 상승.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1216000</v>
+        <v>1213000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.03%</t>
+          <t>'-6.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="G14" t="n">
-        <v>1687</v>
+        <v>1832</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1714,7 +1714,7 @@
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2315411282500</v>
+        <v>2351696855000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 논란과 시장 불확실성으로 주가 급락. 투자자들의 실망감 표출.</t>
+          <t>정치적 이슈와 경영진 관련 논란으로 인한 시장 불신 및 주가 하락 우려. 노후 자금 손실에 대한 답답함 토로.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치적 논란', '주가 급락', '투자자 실망']</t>
+          <t>['주가 하락', '정치적 이슈', '투심']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13940</v>
+        <v>13260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.94%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>198</v>
+        <v>534</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K15" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L15" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M15" t="n">
-        <v>13550</v>
+        <v>13250</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>80116831770</v>
+        <v>112974615550</v>
       </c>
       <c r="P15" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R15" t="n">
-        <v>-51000</v>
+        <v>-506000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>EUV용 유리기판 제조 기술 확보 소식으로 AI 광통신 관련 기대감 상승. 삼성전자 인수 루머 및 기술력에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9980</v>
+        <v>10010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.41%</t>
+          <t>'-10.14%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>60534843645</v>
+        <v>61117681645</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>HT로보틱스, 급등 후 조정 및 투자주의 종목 지정으로 인한 하락세. ESS 마진율 불확실성 언급.</t>
+          <t>급격한 상승 후 조정 국면에 대한 우려와 투자 경고. 외국인 허매수 의혹 및 높은 신용 비율로 인한 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투자주의', '주가 조정', 'ESS 마진율']</t>
+          <t>['급락', '투경', '신용 비율']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261022_14.xlsx
+++ b/data/trending_integrated_20261022_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3662</v>
+        <v>3665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.51%</t>
+          <t>'+18.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F2" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G2" t="n">
-        <v>763</v>
+        <v>780</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>81255606792</v>
+        <v>82018942239</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -619,10 +619,10 @@
         <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-246000</v>
+        <v>-242000</v>
       </c>
       <c r="S2" t="n">
-        <v>195000</v>
+        <v>197000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55600</v>
+        <v>55700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.56%</t>
+          <t>'+16.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
-        <v>1390</v>
+        <v>1423</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>569080109050</v>
+        <v>582741227600</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,10 +711,10 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>1412000</v>
+        <v>1415000</v>
       </c>
       <c r="S3" t="n">
-        <v>520000</v>
+        <v>541000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7390</v>
+        <v>7260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.96%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9161484460</v>
+        <v>9247673450</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -803,7 +803,7 @@
         <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>24000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>22416693408</v>
+        <v>22479691196</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -895,7 +895,7 @@
         <v>1115</v>
       </c>
       <c r="R5" t="n">
-        <v>-71000</v>
+        <v>-66000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1685</v>
+        <v>1658</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.00%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>28019066672</v>
+        <v>28446259431</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -987,7 +987,7 @@
         <v>735</v>
       </c>
       <c r="R6" t="n">
-        <v>22000</v>
+        <v>-49000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7290</v>
+        <v>7300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F7" t="n">
         <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="H7" t="n">
         <v>25.47</v>
@@ -1061,7 +1061,7 @@
         <v>7270</v>
       </c>
       <c r="L7" t="n">
-        <v>7340</v>
+        <v>7350</v>
       </c>
       <c r="M7" t="n">
         <v>7120</v>
@@ -1070,7 +1070,7 @@
         <v>25.45</v>
       </c>
       <c r="O7" t="n">
-        <v>15522199325</v>
+        <v>16703094355</v>
       </c>
       <c r="P7" t="n">
         <v>17950</v>
@@ -1079,23 +1079,23 @@
         <v>7120</v>
       </c>
       <c r="R7" t="n">
-        <v>-148000</v>
+        <v>-80000</v>
       </c>
       <c r="S7" t="n">
-        <v>-69000</v>
+        <v>-92000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>분기 순이익 7천억 달성에도 불구하고 주가 부진. 실적 개선세와 저평가 가능성 언급, 30년 최저가 근접 상황.</t>
+          <t>적자에서 흑자 전환 및 대규모 당기순이익 달성으로 인한 주가 상승 기대감. 실적 개선 기반 턴어라운드 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흑자 전환', '당기순이익', '실적 개선']</t>
+          <t>['흑자전환', '당기순이익', '실적개선']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14640</v>
+        <v>14620</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.88%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>38161231105</v>
+        <v>38610000235</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1171,10 +1171,10 @@
         <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>15000</v>
+        <v>97000</v>
       </c>
       <c r="S8" t="n">
-        <v>-63000</v>
+        <v>-79000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17620</v>
+        <v>41400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.67%</t>
+          <t>'-2.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>874</v>
       </c>
       <c r="H9" t="n">
-        <v>3.29</v>
+        <v>13.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17920</v>
+        <v>42350</v>
       </c>
       <c r="K9" t="n">
-        <v>19180</v>
+        <v>41850</v>
       </c>
       <c r="L9" t="n">
-        <v>20150</v>
+        <v>42350</v>
       </c>
       <c r="M9" t="n">
-        <v>17590</v>
+        <v>41150</v>
       </c>
       <c r="N9" t="n">
-        <v>3.61</v>
+        <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>74272236560</v>
+        <v>12969694700</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-37000</v>
+        <v>47000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
+          <t>간암 신약 승인 기대감 속 기관 수급 확인 및 진회장 발언 기반 긍정 전망. FDA 승인 요건 미충족 및 언론 부정적 시각 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
+          <t>['간암승인', 'FDA', '기관수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41350</v>
+        <v>9900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.14</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>854</v>
+        <v>377</v>
       </c>
       <c r="H10" t="n">
-        <v>13.09</v>
+        <v>5.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42350</v>
+        <v>10190</v>
       </c>
       <c r="K10" t="n">
-        <v>41850</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>42350</v>
+        <v>10180</v>
       </c>
       <c r="M10" t="n">
-        <v>41150</v>
+        <v>9620</v>
       </c>
       <c r="N10" t="n">
-        <v>13.23</v>
+        <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>12657920550</v>
+        <v>17337239675</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>14940</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>5390</v>
       </c>
       <c r="R10" t="n">
-        <v>46000</v>
+        <v>-10000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 속 기관 매수세 유입 관찰. C2 발표 가능성 및 클래스 1 기대감 언급, 시장의 흔들림에 대한 경계.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 기반 주가 상승 기대. 개미 털기 구간 분석 및 큰손 입성 추정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 치료제', '기대감']</t>
+          <t>['테슬라', '스페이스X', '개미털기']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9880</v>
+        <v>17210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-3.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>-0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>374</v>
+        <v>134</v>
       </c>
       <c r="H11" t="n">
-        <v>5.87</v>
+        <v>3.29</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10190</v>
+        <v>17920</v>
       </c>
       <c r="K11" t="n">
-        <v>10110</v>
+        <v>19180</v>
       </c>
       <c r="L11" t="n">
-        <v>10180</v>
+        <v>20150</v>
       </c>
       <c r="M11" t="n">
-        <v>9620</v>
+        <v>17150</v>
       </c>
       <c r="N11" t="n">
-        <v>5.34</v>
+        <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>17007785585</v>
+        <v>76049550275</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>6320</v>
       </c>
       <c r="R11" t="n">
-        <v>-56000</v>
+        <v>-20000</v>
       </c>
       <c r="S11" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조 및 스페이스X 뉴스 관련 기대감과 매물 출회에 따른 혼조세.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '실적', '스페이스X']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213500</v>
+        <v>213750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.47%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="G12" t="n">
-        <v>1645</v>
+        <v>1657</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1813787252750</v>
+        <v>1851898986250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1539,23 +1539,23 @@
         <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-1004000</v>
+        <v>-1112000</v>
       </c>
       <c r="S12" t="n">
-        <v>-549000</v>
+        <v>-410000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 하락에도 정부의 대책 부재와 정치적 이슈로 인한 시장 불신 심화. 엔비디아, 마이크론 등 해외 증시와 상반된 국내 증시 흐름 지적.</t>
+          <t>정부 정책 및 경제 상황에 대한 불만과 주가 하락에 대한 우려 표현. 외인 매도 및 국내 증시 부진 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 폭락', '정부 대책', '국내 증시']</t>
+          <t>['주가폭락', '정부대책', '국내증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14290</v>
+        <v>14270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.61%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H13" t="n">
         <v>1.2</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>81374872945</v>
+        <v>82032023665</v>
       </c>
       <c r="P13" t="n">
         <v>28800</v>
@@ -1631,7 +1631,7 @@
         <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>-54000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1213000</v>
+        <v>1212000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.26%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G14" t="n">
-        <v>1832</v>
+        <v>1924</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1714,7 +1714,7 @@
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2351696855000</v>
+        <v>2384272653000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,23 +1723,23 @@
         <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-62000</v>
+        <v>-178000</v>
       </c>
       <c r="S14" t="n">
-        <v>-88000</v>
+        <v>-66000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 경영진 관련 논란으로 인한 시장 불신 및 주가 하락 우려. 노후 자금 손실에 대한 답답함 토로.</t>
+          <t>정치적 이슈와 연계된 강한 주가 하락 우려 및 정부 정책 비판. 솔리다임 상장 관련 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치적 이슈', '투심']</t>
+          <t>['주가하락', '탄핵', '솔리다임']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13260</v>
+        <v>13300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-7.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.33</v>
       </c>
       <c r="E15" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="H15" t="n">
         <v>3.48</v>
@@ -1806,7 +1806,7 @@
         <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>112974615550</v>
+        <v>114482001635</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,23 +1815,23 @@
         <v>1640</v>
       </c>
       <c r="R15" t="n">
-        <v>-506000</v>
+        <v>-354000</v>
       </c>
       <c r="S15" t="n">
-        <v>-3000</v>
+        <v>-155000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 소식으로 AI 광통신 관련 기대감 상승. 삼성전자 인수 루머 및 기술력에 대한 긍정적 전망.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 기반 주가 상승 기대. 나스닥 선물 동향 및 프로그램 매도세 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['EUV', '유리기판', 'AI광통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10010</v>
+        <v>9930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.14%</t>
+          <t>'-10.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F16" t="n">
         <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>61117681645</v>
+        <v>61682869950</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1907,23 +1907,23 @@
         <v>2270</v>
       </c>
       <c r="R16" t="n">
-        <v>-205000</v>
+        <v>-201000</v>
       </c>
       <c r="S16" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>급격한 상승 후 조정 국면에 대한 우려와 투자 경고. 외국인 허매수 의혹 및 높은 신용 비율로 인한 추가 하락 가능성 제기.</t>
+          <t>투경(투자경고) 종목 지정 및 급격한 주가 하락 우려. ESS 마진율 불확실성 및 신용 비율 높은 점 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['급락', '투경', '신용 비율']</t>
+          <t>['투경', '주가하락', 'ESS']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261022_14.xlsx
+++ b/data/trending_integrated_20261022_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>3690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.61%</t>
+          <t>'+19.42%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F2" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G2" t="n">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>82018942239</v>
+        <v>82717558542</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55700</v>
+        <v>55300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.77%</t>
+          <t>'+15.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
-        <v>1423</v>
+        <v>1444</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>582741227600</v>
+        <v>589005743400</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 시장 기대 뛰어넘는 어닝 서프라이즈 발표. MSCI 편입 예상 및 자사주 취득 공시로 강세 전망.</t>
+          <t>어닝 서프라이즈 발표, 자사주 취득 및 공매도 관련 긍정적 뉴스. MSCI 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9247673450</v>
+        <v>9299133980</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.22%</t>
+          <t>'+4.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>22479691196</v>
+        <v>22675320114</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>푸드나무, 주가 조작 의혹 및 보호예수 해제 물량에 대한 우려. 일부 긍정적 기대감 존재.</t>
+          <t>보호예수 해제 물량 및 주가조작 의혹 언급. 긍정적 호재와 단기 차익 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 조작', '보호예수', '호재']</t>
+          <t>['보호예수 해제', '주가 조작', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1658</v>
+        <v>1669</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+1.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>28446259431</v>
+        <v>28678556163</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7300</v>
+        <v>7290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="H7" t="n">
         <v>25.47</v>
@@ -1070,7 +1070,7 @@
         <v>25.45</v>
       </c>
       <c r="O7" t="n">
-        <v>16703094355</v>
+        <v>17512693915</v>
       </c>
       <c r="P7" t="n">
         <v>17950</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>적자에서 흑자 전환 및 대규모 당기순이익 달성으로 인한 주가 상승 기대감. 실적 개선 기반 턴어라운드 전망.</t>
+          <t>적자에서 흑자 전환 및 순이익 증가 등 긍정적 실적 발표. 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흑자전환', '당기순이익', '실적개선']</t>
+          <t>['흑자 전환', '순이익', '실적 발표']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14620</v>
+        <v>14580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>14580</v>
       </c>
       <c r="N8" t="n">
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>38610000235</v>
+        <v>39426002310</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
+          <t>실적 우량주 언급과 함께 외국인·연기금 매수세 포착. 정치 관련 언급 및 삼성E&amp;A와의 비교.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외국인 매수', '건설주', '대차해지']</t>
+          <t>['건설주', '외국인 매수', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41400</v>
+        <v>9950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.24%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>874</v>
+        <v>378</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>5.87</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>10190</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>10110</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>10180</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>9620</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>5.34</v>
       </c>
       <c r="O9" t="n">
-        <v>12969694700</v>
+        <v>17571232805</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>14940</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>5390</v>
       </c>
       <c r="R9" t="n">
-        <v>47000</v>
+        <v>-10000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 신약 승인 기대감 속 기관 수급 확인 및 진회장 발언 기반 긍정 전망. FDA 승인 요건 미충족 및 언론 부정적 시각 우려.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 기반 주가 상승 기대. 개미 털기 구간 분석 및 큰손 입성 추정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['간암승인', 'FDA', '기관수급']</t>
+          <t>['테슬라', '스페이스X', '개미털기']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9900</v>
+        <v>41300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>377</v>
+        <v>889</v>
       </c>
       <c r="H10" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K10" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L10" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M10" t="n">
-        <v>9620</v>
+        <v>41150</v>
       </c>
       <c r="N10" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>17337239675</v>
+        <v>13275934125</v>
       </c>
       <c r="P10" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-10000</v>
+        <v>47000</v>
       </c>
       <c r="S10" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 기반 주가 상승 기대. 개미 털기 구간 분석 및 큰손 입성 추정.</t>
+          <t>간암 신약 승인 기대감 속 기관 수급 확인 및 진회장 발언 기반 긍정 전망. FDA 승인 요건 미충족 및 언론 부정적 시각 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '개미털기']</t>
+          <t>['간암승인', 'FDA', '기관수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17210</v>
+        <v>17330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.96%</t>
+          <t>'-3.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
         <v>3.29</v>
@@ -1438,7 +1438,7 @@
         <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>76049550275</v>
+        <v>77025383175</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213750</v>
+        <v>14300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-4.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="F12" t="n">
-        <v>526</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>1657</v>
+        <v>211</v>
       </c>
       <c r="H12" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L12" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M12" t="n">
-        <v>213000</v>
+        <v>13550</v>
       </c>
       <c r="N12" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1851898986250</v>
+        <v>82424119945</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R12" t="n">
-        <v>-1112000</v>
+        <v>-54000</v>
       </c>
       <c r="S12" t="n">
-        <v>-410000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정부 정책 및 경제 상황에 대한 불만과 주가 하락에 대한 우려 표현. 외인 매도 및 국내 증시 부진 언급.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,112 +1555,112 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가폭락', '정부대책', '국내증시']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14270</v>
+        <v>213000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>520</v>
       </c>
       <c r="G13" t="n">
-        <v>209</v>
+        <v>1640</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>46.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>223500</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>221500</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>226000</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>213000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>46.08</v>
       </c>
       <c r="O13" t="n">
-        <v>82032023665</v>
+        <v>1883184241500</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>94500</v>
       </c>
       <c r="R13" t="n">
-        <v>-54000</v>
+        <v>-1112000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-410000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>정부 정책 및 정치 이슈 관련 부정적 언급 다수. 실적 대비 주가 부진 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['정부 정책', '주가 부진', '외국인 매매']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1212000</v>
+        <v>1209000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="G14" t="n">
-        <v>1924</v>
+        <v>1972</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1714,7 +1714,7 @@
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2384272653000</v>
+        <v>2420542671500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 강한 주가 하락 우려 및 정부 정책 비판. 솔리다임 상장 관련 주가 하락 가능성 언급.</t>
+          <t>정치 및 정부 정책 관련 부정적 발언 다수. 반도체 산업 전반의 불확실성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가하락', '탄핵', '솔리다임']</t>
+          <t>['정치 이슈', '주가 하락', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13300</v>
+        <v>13260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.06%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.33</v>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="H15" t="n">
         <v>3.48</v>
@@ -1806,7 +1806,7 @@
         <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>114482001635</v>
+        <v>115689444310</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9930</v>
+        <v>10020</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.86%</t>
+          <t>'-10.05%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>61682869950</v>
+        <v>62425615285</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>투경(투자경고) 종목 지정 및 급격한 주가 하락 우려. ESS 마진율 불확실성 및 신용 비율 높은 점 지적.</t>
+          <t>주가 급락 및 조정에 대한 부정적 의견. 투자 경고 및 신용 사용 자제 권고.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투경', '주가하락', 'ESS']</t>
+          <t>['주가 급락', '조정', '투기']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261022_14.xlsx
+++ b/data/trending_integrated_20261022_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3690</v>
+        <v>3715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.42%</t>
+          <t>'+20.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F2" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G2" t="n">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>82717558542</v>
+        <v>86090324844</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55300</v>
+        <v>55000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.93%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G3" t="n">
-        <v>1444</v>
+        <v>1483</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>589005743400</v>
+        <v>598834174400</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>어닝 서프라이즈 발표, 자사주 취득 및 공매도 관련 긍정적 뉴스. MSCI 편입 예상.</t>
+          <t>실적 발표 및 어닝 서프라이즈, 자사주 취득 공시로 강한 상승세 전망. MSCI 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7260</v>
+        <v>7290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+9.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9299133980</v>
+        <v>9343259420</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1677</v>
+        <v>1696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.16%</t>
+          <t>'+5.34%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>22675320114</v>
+        <v>22887716700</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1669</v>
+        <v>1627</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.03%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>28678556163</v>
+        <v>29032322923</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7290</v>
+        <v>7230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="H7" t="n">
         <v>25.47</v>
@@ -1070,7 +1070,7 @@
         <v>25.45</v>
       </c>
       <c r="O7" t="n">
-        <v>17512693915</v>
+        <v>18346749825</v>
       </c>
       <c r="P7" t="n">
         <v>17950</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14580</v>
+        <v>14500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>142</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>14580</v>
+        <v>14490</v>
       </c>
       <c r="N8" t="n">
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>39426002310</v>
+        <v>40661946815</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9950</v>
+        <v>41400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="G9" t="n">
-        <v>378</v>
+        <v>894</v>
       </c>
       <c r="H9" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K9" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L9" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M9" t="n">
-        <v>9620</v>
+        <v>41150</v>
       </c>
       <c r="N9" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>17571232805</v>
+        <v>13842073425</v>
       </c>
       <c r="P9" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-10000</v>
+        <v>47000</v>
       </c>
       <c r="S9" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 기반 주가 상승 기대. 개미 털기 구간 분석 및 큰손 입성 추정.</t>
+          <t>간암 치료제 FDA 승인 기대감 속 주가 변동성. Class 2 예상 및 C2 수령 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '개미털기']</t>
+          <t>['FDA 승인', '간암 치료제', '주가 변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41300</v>
+        <v>9890</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.14</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>889</v>
+        <v>391</v>
       </c>
       <c r="H10" t="n">
-        <v>13.09</v>
+        <v>5.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42350</v>
+        <v>10190</v>
       </c>
       <c r="K10" t="n">
-        <v>41850</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>42350</v>
+        <v>10180</v>
       </c>
       <c r="M10" t="n">
-        <v>41150</v>
+        <v>9620</v>
       </c>
       <c r="N10" t="n">
-        <v>13.23</v>
+        <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>13275934125</v>
+        <v>17860778765</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>14940</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>5390</v>
       </c>
       <c r="R10" t="n">
-        <v>47000</v>
+        <v>-10000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>간암 신약 승인 기대감 속 기관 수급 확인 및 진회장 발언 기반 긍정 전망. FDA 승인 요건 미충족 및 언론 부정적 시각 우려.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 긍정적. 지수 하락 속에서 개별 이슈로 인한 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['간암승인', 'FDA', '기관수급']</t>
+          <t>['테슬라', '스페이스X', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17330</v>
+        <v>17220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.29%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F11" t="n">
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H11" t="n">
         <v>3.29</v>
@@ -1432,13 +1432,13 @@
         <v>20150</v>
       </c>
       <c r="M11" t="n">
-        <v>17150</v>
+        <v>17060</v>
       </c>
       <c r="N11" t="n">
         <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>77025383175</v>
+        <v>78324170075</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14300</v>
+        <v>213000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>520</v>
       </c>
       <c r="G12" t="n">
-        <v>211</v>
+        <v>1549</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14980</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>14460</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>16140</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>13550</v>
+        <v>212000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>82424119945</v>
+        <v>1973545852750</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>12030</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-54000</v>
+        <v>-1112000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-410000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>정부 정책 및 증시 상황에 대한 부정적 여론 고조. 실적 대비 주가 부진.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['정부 정책', '주가 부진', '증시 상황']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>213000</v>
+        <v>14120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-5.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>1640</v>
+        <v>212</v>
       </c>
       <c r="H13" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>213000</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1883184241500</v>
+        <v>82949364755</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-1112000</v>
+        <v>-54000</v>
       </c>
       <c r="S13" t="n">
-        <v>-410000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치 이슈 관련 부정적 언급 다수. 실적 대비 주가 부진 지적.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정부 정책', '주가 부진', '외국인 매매']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1209000</v>
+        <v>1211000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.57%</t>
+          <t>'-6.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="G14" t="n">
-        <v>1972</v>
+        <v>1926</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1714,7 +1714,7 @@
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2420542671500</v>
+        <v>2492441446000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치 및 정부 정책 관련 부정적 발언 다수. 반도체 산업 전반의 불확실성 언급.</t>
+          <t>정치권 및 경영진에 대한 강한 불만 표출. 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치 이슈', '주가 하락', '반도체']</t>
+          <t>['정치권 불만', '주가 하락', '경영진']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13260</v>
+        <v>13270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-7.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.33</v>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
-        <v>573</v>
+        <v>616</v>
       </c>
       <c r="H15" t="n">
         <v>3.48</v>
@@ -1800,13 +1800,13 @@
         <v>14830</v>
       </c>
       <c r="M15" t="n">
-        <v>13250</v>
+        <v>13240</v>
       </c>
       <c r="N15" t="n">
         <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>115689444310</v>
+        <v>117068802150</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 기반 주가 상승 기대. 나스닥 선물 동향 및 프로그램 매도세 주시.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 삼성 인수설 등으로 인한 기대감 형성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['EUV', '유리기판', 'AI광통신']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10020</v>
+        <v>10030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.05%</t>
+          <t>'-9.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G16" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>62425615285</v>
+        <v>63567947130</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
